--- a/outputs/etf_trend_strategy/threshold_0.9/threshold_0.9/window_15/return_r2/staggered_7d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/threshold_0.9/window_15/return_r2/staggered_7d/close/close_annual_metrics.xlsx
@@ -468,10 +468,10 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.0796128181535436</v>
+        <v>0.1418025791307107</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.1036282963047599</v>
+        <v>0.1672014391952032</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.3230890067363991</v>
+        <v>0.2600693443292972</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2685982858885862</v>
+        <v>0.1926847072228469</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.3827026143982913</v>
+        <v>0.6486671718415469</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.5552071455225021</v>
+        <v>0.9387363426144802</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.5482500310058338</v>
+        <v>0.9980577070474033</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.2362748921174107</v>
+        <v>0.1974672080644986</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1631554965233102</v>
+        <v>0.1079514562191319</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.3826957854633162</v>
+        <v>0.8186865294463965</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>23.09272125979042</v>
+        <v>26.28971317587167</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1555057597633354</v>
+        <v>-0.1515164378811886</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.09048247546749622</v>
+        <v>0.09563382570082024</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2809600747844308</v>
+        <v>0.2503377818954447</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1920935880383719</v>
+        <v>0.1550295846288512</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.5392413631477398</v>
+        <v>-0.6177145901856591</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-0.7441466006599171</v>
+        <v>-0.8343552329063746</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.5610205305359071</v>
+        <v>0.6749449809186696</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2459848494408262</v>
+        <v>0.214033955232121</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1348534904279416</v>
+        <v>0.09820882987649027</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.6560701533470031</v>
+        <v>-0.7347322915530844</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>22.68196123903819</v>
+        <v>24.69622639333934</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.205192500681338</v>
+        <v>-0.1459836202078574</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.1027540014706895</v>
+        <v>-0.03591400420371171</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.2546860027827653</v>
+        <v>0.2117462323729114</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1948416422749349</v>
+        <v>0.1426110780004884</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.8703888986286048</v>
+        <v>-0.7408056991621341</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-1.234600346452786</v>
+        <v>-1.044870986908357</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.4603608196477395</v>
+        <v>-0.1744913841746915</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.3127093963969931</v>
+        <v>0.2719765512157142</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1845092468691176</v>
+        <v>0.1299245339080871</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.6801825025326882</v>
+        <v>-0.5571598962343178</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>27.23074993947298</v>
+        <v>26.99871391116838</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.05541993927768873</v>
+        <v>-0.03056995859254508</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.1639457604673176</v>
+        <v>-0.1419508734608819</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.3141379034133896</v>
+        <v>0.2576596595989069</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1756732056776913</v>
+        <v>0.1300763032445363</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.08250328419101095</v>
+        <v>-0.05643039396515463</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.1351728815082559</v>
+        <v>-0.08976188538851532</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.9322554522009273</v>
+        <v>-1.171579506620507</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2695087516281272</v>
+        <v>0.2682936595884028</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.199445332227237</v>
+        <v>0.2016991451691948</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.2138807577198428</v>
+        <v>-0.1185748276096476</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>26.35097672941629</v>
+        <v>27.95039465996716</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.32386891755666</v>
+        <v>0.2945340052904688</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.08130927647394159</v>
+        <v>0.05734911520923958</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.3100248213870291</v>
+        <v>0.2452142259169329</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1941713794496641</v>
+        <v>0.1268934663692843</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.046099372852919</v>
+        <v>1.154248946083586</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.514716289707923</v>
+        <v>1.667426284300338</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.5932720512406587</v>
+        <v>0.5825196938881624</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.2033350447254639</v>
+        <v>0.1797810830785402</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1826171543195292</v>
+        <v>0.1418798250884112</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.660791089057849</v>
+        <v>1.707468775498784</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>26.21138867962669</v>
+        <v>28.4259436035863</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.2028112128908925</v>
+        <v>0.236684826294111</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.2211795044403295</v>
+        <v>0.2555704063424855</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.3769145011738559</v>
+        <v>0.3032631873161919</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2520582858595225</v>
+        <v>0.1849689910027504</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.044049704805541</v>
+        <v>1.381918935840011</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.475339128040193</v>
+        <v>1.997660091800965</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.625978050860992</v>
+        <v>2.353956224731229</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1372087766933431</v>
+        <v>0.1134918422615231</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1005337417139885</v>
+        <v>0.06852799958063771</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.922774928992855</v>
+        <v>4.175779927484369</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>23.85399227213802</v>
+        <v>27.71588286350791</v>
       </c>
     </row>
   </sheetData>
